--- a/Data Input Pengujian/data.xlsx
+++ b/Data Input Pengujian/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python\odooCompressionTest\Data Input Pengujian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{642CAFBF-97CF-4E33-A6B1-DD755D7AF778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20762F44-3352-46ED-A5BC-7AF78D299752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="55">
   <si>
     <t>Tanggal</t>
   </si>
@@ -52,31 +52,142 @@
     <t>Kode Benda Uji</t>
   </si>
   <si>
-    <t>13-01-2026</t>
-  </si>
-  <si>
-    <t>TATA / K 400 / AD PTB</t>
-  </si>
-  <si>
-    <t>VINFAST INTERNAL ROAD PACKAGE 1</t>
+    <t xml:space="preserve"> Slump 12.0 +2.0/-2.0</t>
+  </si>
+  <si>
+    <t>TM 944</t>
+  </si>
+  <si>
+    <t>Patimban Port Development Project Package 6 : Container Terminal No.2 Construction</t>
+  </si>
+  <si>
+    <t>Class A-2 NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slump 5.0 +5.0/-0.0</t>
+  </si>
+  <si>
+    <t>JALAN TOL AKSES PATIMBAN PAKET 4</t>
+  </si>
+  <si>
+    <t>TM 852</t>
+  </si>
+  <si>
+    <t>Class B-2 NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slump 55.0 +10.0/-0.0</t>
+  </si>
+  <si>
+    <t>AGUS</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04655</t>
+  </si>
+  <si>
+    <t>HK - JAKON JO / PILEHEAD R11 - R15 OP 6 STA 32+048 / CLASS B-1 / AD PTB</t>
+  </si>
+  <si>
+    <t>Pembangunan Jalan Tol Akses Patimban Paket 3</t>
   </si>
   <si>
     <t>TAUFIQ</t>
   </si>
   <si>
-    <t>K-400 FA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Slump 12.0 +1.5/-1.5</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/01-2026/00445</t>
-  </si>
-  <si>
-    <t>TM 601</t>
-  </si>
-  <si>
-    <t>13-01-2026 16:44:35</t>
+    <t>Class B-1 FA</t>
+  </si>
+  <si>
+    <t>TM 590</t>
+  </si>
+  <si>
+    <t>2026-06-02 19:19:08</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04658</t>
+  </si>
+  <si>
+    <t>2026-06-02 20:02:32</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04665</t>
+  </si>
+  <si>
+    <t>TM 902</t>
+  </si>
+  <si>
+    <t>2026-06-02 21:30:19</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04628</t>
+  </si>
+  <si>
+    <t>PTRPWJ / RIGID PAV - 14164 / CLASS A-2 / AD PTB</t>
+  </si>
+  <si>
+    <t>2026-06-02 14:42:48</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04632</t>
+  </si>
+  <si>
+    <t>TM 894</t>
+  </si>
+  <si>
+    <t>2026-06-02 15:28:20</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04638</t>
+  </si>
+  <si>
+    <t>2026-06-02 16:28:33</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04648</t>
+  </si>
+  <si>
+    <t>2026-06-02 18:08:44</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04661</t>
+  </si>
+  <si>
+    <t>2026-06-02 20:46:50</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04669</t>
+  </si>
+  <si>
+    <t>2026-06-02 21:59:53</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04641</t>
+  </si>
+  <si>
+    <t>WIKA - ADHI JO / BP P1 1A MB21 / CLASS B-2 SCC / AD PTB</t>
+  </si>
+  <si>
+    <t>NANDA</t>
+  </si>
+  <si>
+    <t>2026-06-02 17:02:51</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04644</t>
+  </si>
+  <si>
+    <t>2026-06-02 17:34:26</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/06-2026/04649</t>
+  </si>
+  <si>
+    <t>TM 813</t>
+  </si>
+  <si>
+    <t>2026-06-02 18:17:02</t>
   </si>
 </sst>
 </file>
@@ -450,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -492,35 +603,358 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="I8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G11" t="s">
         <v>17</v>
       </c>
+      <c r="H11" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Data Input Pengujian/data.xlsx
+++ b/Data Input Pengujian/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python\odooCompressionTest\Data Input Pengujian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20762F44-3352-46ED-A5BC-7AF78D299752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072FED4A-1968-44F6-A4D3-2B133BE0CECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Tanggal</t>
   </si>
@@ -55,139 +55,61 @@
     <t xml:space="preserve"> Slump 12.0 +2.0/-2.0</t>
   </si>
   <si>
-    <t>TM 944</t>
-  </si>
-  <si>
-    <t>Patimban Port Development Project Package 6 : Container Terminal No.2 Construction</t>
-  </si>
-  <si>
-    <t>Class A-2 NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Slump 5.0 +5.0/-0.0</t>
+    <t>TM 631</t>
+  </si>
+  <si>
+    <t>TM 894</t>
+  </si>
+  <si>
+    <t>AGUS</t>
+  </si>
+  <si>
+    <t>TATA / K 400 / AD PTB</t>
+  </si>
+  <si>
+    <t>VINFAST INDONESIA FACTORY (RC PHASE 2)</t>
+  </si>
+  <si>
+    <t>K-400 NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slump 12.0 +1.5/-1.5</t>
   </si>
   <si>
     <t>JALAN TOL AKSES PATIMBAN PAKET 4</t>
   </si>
   <si>
-    <t>TM 852</t>
-  </si>
-  <si>
-    <t>Class B-2 NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Slump 55.0 +10.0/-0.0</t>
-  </si>
-  <si>
-    <t>AGUS</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04655</t>
-  </si>
-  <si>
-    <t>HK - JAKON JO / PILEHEAD R11 - R15 OP 6 STA 32+048 / CLASS B-1 / AD PTB</t>
-  </si>
-  <si>
-    <t>Pembangunan Jalan Tol Akses Patimban Paket 3</t>
-  </si>
-  <si>
-    <t>TAUFIQ</t>
-  </si>
-  <si>
-    <t>Class B-1 FA</t>
-  </si>
-  <si>
-    <t>TM 590</t>
-  </si>
-  <si>
-    <t>2026-06-02 19:19:08</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04658</t>
-  </si>
-  <si>
-    <t>2026-06-02 20:02:32</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04665</t>
-  </si>
-  <si>
-    <t>TM 902</t>
-  </si>
-  <si>
-    <t>2026-06-02 21:30:19</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04628</t>
-  </si>
-  <si>
-    <t>PTRPWJ / RIGID PAV - 14164 / CLASS A-2 / AD PTB</t>
-  </si>
-  <si>
-    <t>2026-06-02 14:42:48</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04632</t>
-  </si>
-  <si>
-    <t>TM 894</t>
-  </si>
-  <si>
-    <t>2026-06-02 15:28:20</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04638</t>
-  </si>
-  <si>
-    <t>2026-06-02 16:28:33</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04648</t>
-  </si>
-  <si>
-    <t>2026-06-02 18:08:44</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04661</t>
-  </si>
-  <si>
-    <t>2026-06-02 20:46:50</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04669</t>
-  </si>
-  <si>
-    <t>2026-06-02 21:59:53</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04641</t>
-  </si>
-  <si>
-    <t>WIKA - ADHI JO / BP P1 1A MB21 / CLASS B-2 SCC / AD PTB</t>
-  </si>
-  <si>
     <t>NANDA</t>
   </si>
   <si>
-    <t>2026-06-02 17:02:51</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04644</t>
-  </si>
-  <si>
-    <t>2026-06-02 17:34:26</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/06-2026/04649</t>
-  </si>
-  <si>
-    <t>TM 813</t>
-  </si>
-  <si>
-    <t>2026-06-02 18:17:02</t>
+    <t>TM 880</t>
+  </si>
+  <si>
+    <t>Class B-1 NFA</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>WIKA - ADHI JO / PLAT INJAK AE1 PS.18 / CLASS B-1 / AD PTB</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/08-2026/08302</t>
+  </si>
+  <si>
+    <t>2026-08-01 17:15:13</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/08-2026/08313</t>
+  </si>
+  <si>
+    <t>2026-08-01 23:41:05</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/08-2026/08314</t>
+  </si>
+  <si>
+    <t>2026-08-01 23:53:12</t>
   </si>
 </sst>
 </file>
@@ -561,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -603,350 +525,89 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
         <v>10</v>
       </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
       <c r="I4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Data Input Pengujian/data.xlsx
+++ b/Data Input Pengujian/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python\odooCompressionTest\Data Input Pengujian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072FED4A-1968-44F6-A4D3-2B133BE0CECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845A1153-38CC-4D36-AE77-6B68D60FC928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="131">
   <si>
     <t>Tanggal</t>
   </si>
@@ -55,61 +55,367 @@
     <t xml:space="preserve"> Slump 12.0 +2.0/-2.0</t>
   </si>
   <si>
+    <t>JALAN TOL AKSES PATIMBAN PAKET 4</t>
+  </si>
+  <si>
+    <t>TAUFIQ</t>
+  </si>
+  <si>
+    <t>DATA</t>
+  </si>
+  <si>
+    <t>JALAN TOL AKSES PATIMBAN</t>
+  </si>
+  <si>
+    <t>Fc-30 NFA</t>
+  </si>
+  <si>
+    <t>TM 648</t>
+  </si>
+  <si>
+    <t>TM 664</t>
+  </si>
+  <si>
     <t>TM 631</t>
   </si>
   <si>
-    <t>TM 894</t>
+    <t>CTB 4% NFA-0 NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slump 0.0 +0.0/-0.0</t>
+  </si>
+  <si>
+    <t>DT EXT 011</t>
+  </si>
+  <si>
+    <t>DT EXT 015</t>
+  </si>
+  <si>
+    <t>DT EXT 005</t>
+  </si>
+  <si>
+    <t>Pembangunan Jalan Tol Akses Patimban Paket 3</t>
+  </si>
+  <si>
+    <t>Class B-1 FA</t>
+  </si>
+  <si>
+    <t>AAM ADI ALAMSYAH</t>
+  </si>
+  <si>
+    <t>Plant Patimban</t>
+  </si>
+  <si>
+    <t>Bukan</t>
+  </si>
+  <si>
+    <t>Ada</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Belum</t>
+  </si>
+  <si>
+    <t>TM 687</t>
+  </si>
+  <si>
+    <t>DENI</t>
+  </si>
+  <si>
+    <t>DACA MARWANTO</t>
+  </si>
+  <si>
+    <t>Plant Readymix Subang</t>
+  </si>
+  <si>
+    <t>TESCO INDOMARITIM / K 350 / AD PTB</t>
+  </si>
+  <si>
+    <t>PT Tesco Indomaritim</t>
+  </si>
+  <si>
+    <t>K-350 NFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slump 14.0 +2.0/-2.0</t>
+  </si>
+  <si>
+    <t>CAHYUDIN AMZAH</t>
+  </si>
+  <si>
+    <t>ODAY</t>
+  </si>
+  <si>
+    <t>OPIK</t>
   </si>
   <si>
     <t>AGUS</t>
   </si>
   <si>
-    <t>TATA / K 400 / AD PTB</t>
-  </si>
-  <si>
-    <t>VINFAST INDONESIA FACTORY (RC PHASE 2)</t>
-  </si>
-  <si>
-    <t>K-400 NFA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Slump 12.0 +1.5/-1.5</t>
-  </si>
-  <si>
-    <t>JALAN TOL AKSES PATIMBAN PAKET 4</t>
-  </si>
-  <si>
-    <t>NANDA</t>
+    <t>OS 011</t>
+  </si>
+  <si>
+    <t>OS 015</t>
+  </si>
+  <si>
+    <t>TM 852</t>
+  </si>
+  <si>
+    <t>NANO SUWARNO</t>
+  </si>
+  <si>
+    <t>UJANG SAPUTRA</t>
+  </si>
+  <si>
+    <t>OS 005</t>
+  </si>
+  <si>
+    <t>HK - JAKON JO / BARRIER A47 - A57 R/L PS.14 STA 30+800 / CLASS B-1 / AD PTB</t>
+  </si>
+  <si>
+    <t>DODI IRAWAN</t>
+  </si>
+  <si>
+    <t>PP - TOL PTB / PILECAPE P2 B7 STA 20+000 / FC 30 / AD PTB</t>
+  </si>
+  <si>
+    <t>TM 944</t>
+  </si>
+  <si>
+    <t>SUGENG</t>
+  </si>
+  <si>
+    <t>HATOMI</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10081</t>
+  </si>
+  <si>
+    <t>2026-09-12 00:27:16</t>
+  </si>
+  <si>
+    <t>2026-09-12 02:00:06</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10126</t>
+  </si>
+  <si>
+    <t>HK - JAKON JO / DECKSLAB PW2 - AW2 BRIGDGE 17 STA 30+700 / CLASS B-1 / AD PTB</t>
   </si>
   <si>
     <t>TM 880</t>
   </si>
   <si>
-    <t>Class B-1 NFA</t>
-  </si>
-  <si>
-    <t>2026-08-01</t>
-  </si>
-  <si>
-    <t>WIKA - ADHI JO / PLAT INJAK AE1 PS.18 / CLASS B-1 / AD PTB</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/08-2026/08302</t>
-  </si>
-  <si>
-    <t>2026-08-01 17:15:13</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/08-2026/08313</t>
-  </si>
-  <si>
-    <t>2026-08-01 23:41:05</t>
-  </si>
-  <si>
-    <t>DOCKET/PTB/08-2026/08314</t>
-  </si>
-  <si>
-    <t>2026-08-01 23:53:12</t>
+    <t>2026-09-12 20:18:27</t>
+  </si>
+  <si>
+    <t>2026-09-12 22:11:13</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10129</t>
+  </si>
+  <si>
+    <t>2026-09-12 20:55:09</t>
+  </si>
+  <si>
+    <t>2026-09-12 23:02:21</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10135</t>
+  </si>
+  <si>
+    <t>2026-09-12 22:26:39</t>
+  </si>
+  <si>
+    <t>2026-09-13 00:14:52</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10140</t>
+  </si>
+  <si>
+    <t>2026-09-12 23:38:14</t>
+  </si>
+  <si>
+    <t>2026-09-13 01:17:08</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10124</t>
+  </si>
+  <si>
+    <t>PP - TOL PTB / APPROACH SLAB BOX CULVERT STA 16+060 / FC 30 / AD PTB</t>
+  </si>
+  <si>
+    <t>2026-09-12 19:31:48</t>
+  </si>
+  <si>
+    <t>2026-09-12 22:00:19</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10125</t>
+  </si>
+  <si>
+    <t>2026-09-12 19:42:48</t>
+  </si>
+  <si>
+    <t>2026-09-12 22:00:24</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10082</t>
+  </si>
+  <si>
+    <t>WARSID</t>
+  </si>
+  <si>
+    <t>2026-09-12 00:35:22</t>
+  </si>
+  <si>
+    <t>2026-09-12 04:33:03</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10084</t>
+  </si>
+  <si>
+    <t>2026-09-12 01:04:56</t>
+  </si>
+  <si>
+    <t>2026-09-12 07:06:14</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10091</t>
+  </si>
+  <si>
+    <t>2026-09-12 08:22:01</t>
+  </si>
+  <si>
+    <t>2026-09-12 12:28:17</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10090</t>
+  </si>
+  <si>
+    <t>2026-09-12 07:20:17</t>
+  </si>
+  <si>
+    <t>2026-09-12 10:24:32</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10093</t>
+  </si>
+  <si>
+    <t>WAWAN SETIAWAN</t>
+  </si>
+  <si>
+    <t>2026-09-12 08:58:00</t>
+  </si>
+  <si>
+    <t>2026-09-12 11:17:03</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10105</t>
+  </si>
+  <si>
+    <t>2026-09-12 11:45:19</t>
+  </si>
+  <si>
+    <t>2026-09-12 14:19:35</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10107</t>
+  </si>
+  <si>
+    <t>2026-09-12 12:38:25</t>
+  </si>
+  <si>
+    <t>2026-09-12 15:28:14</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10094</t>
+  </si>
+  <si>
+    <t>WIKA - ADHI JO / STA 34+904 L1 / CTB 4% / AD PTB</t>
+  </si>
+  <si>
+    <t>ARDIAN</t>
+  </si>
+  <si>
+    <t>2026-09-12 09:19:34</t>
+  </si>
+  <si>
+    <t>2026-09-12 10:13:26</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10097</t>
+  </si>
+  <si>
+    <t>2026-09-12 09:40:34</t>
+  </si>
+  <si>
+    <t>2026-09-12 10:26:46</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10101</t>
+  </si>
+  <si>
+    <t>2026-09-12 10:38:20</t>
+  </si>
+  <si>
+    <t>2026-09-12 11:29:08</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10108</t>
+  </si>
+  <si>
+    <t>2026-09-12 13:24:30</t>
+  </si>
+  <si>
+    <t>2026-09-12 14:19:02</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10112</t>
+  </si>
+  <si>
+    <t>2026-09-12 14:18:37</t>
+  </si>
+  <si>
+    <t>2026-09-12 15:27:48</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10117</t>
+  </si>
+  <si>
+    <t>2026-09-12 15:33:04</t>
+  </si>
+  <si>
+    <t>2026-09-12 17:52:05</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10113</t>
+  </si>
+  <si>
+    <t>WIKA - ADHI JO / STA 35+625 L / CLASS E / AD PTB</t>
+  </si>
+  <si>
+    <t>Class E-1 NFA</t>
+  </si>
+  <si>
+    <t>2026-09-12 14:27:14</t>
+  </si>
+  <si>
+    <t>2026-09-12 17:48:55</t>
+  </si>
+  <si>
+    <t>DOCKET/PTB/09-2026/10118</t>
+  </si>
+  <si>
+    <t>2026-09-12 16:22:07</t>
+  </si>
+  <si>
+    <t>2026-09-12 17:49:06</t>
   </si>
 </sst>
 </file>
@@ -483,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -494,7 +800,7 @@
     <col min="9" max="9" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,91 +829,1302 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
       <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2">
+        <v>6</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3">
+        <v>7</v>
+      </c>
+      <c r="M3">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4">
+        <v>7</v>
+      </c>
+      <c r="M4">
+        <v>7</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+      <c r="P4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>28</v>
+      </c>
+      <c r="R4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>7</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P5" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>28</v>
+      </c>
+      <c r="R5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6">
+        <v>7</v>
+      </c>
+      <c r="M6">
+        <v>7</v>
+      </c>
+      <c r="N6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+      <c r="P6" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>11</v>
       </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7">
+        <v>7</v>
+      </c>
+      <c r="N7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" t="s">
+        <v>75</v>
+      </c>
+      <c r="P7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8">
+        <v>7</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" t="s">
+        <v>78</v>
+      </c>
+      <c r="P8" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>28</v>
+      </c>
+      <c r="R8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9">
+        <v>7</v>
+      </c>
+      <c r="M9">
+        <v>7</v>
+      </c>
+      <c r="N9" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" t="s">
+        <v>82</v>
+      </c>
+      <c r="P9" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10">
+        <v>7</v>
+      </c>
+      <c r="M10">
+        <v>7</v>
+      </c>
+      <c r="N10" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11">
+        <v>7</v>
+      </c>
+      <c r="M11">
+        <v>7</v>
+      </c>
+      <c r="N11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" t="s">
+        <v>88</v>
+      </c>
+      <c r="P11" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>28</v>
+      </c>
+      <c r="R11" t="s">
+        <v>29</v>
+      </c>
+      <c r="S11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>33</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12">
+        <v>7</v>
+      </c>
+      <c r="M12">
+        <v>7</v>
+      </c>
+      <c r="N12" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" t="s">
+        <v>29</v>
+      </c>
+      <c r="S12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>94</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13">
+        <v>7</v>
+      </c>
+      <c r="M13">
+        <v>7</v>
+      </c>
+      <c r="N13" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" t="s">
+        <v>95</v>
+      </c>
+      <c r="P13" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="s">
+        <v>50</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14">
+        <v>7</v>
+      </c>
+      <c r="M14">
+        <v>7</v>
+      </c>
+      <c r="N14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" t="s">
+        <v>98</v>
+      </c>
+      <c r="P14" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>28</v>
+      </c>
+      <c r="R14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15">
+        <v>7</v>
+      </c>
+      <c r="M15">
+        <v>7</v>
+      </c>
+      <c r="N15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" t="s">
+        <v>101</v>
+      </c>
+      <c r="P15" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>105</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16">
+        <v>10</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" t="s">
+        <v>106</v>
+      </c>
+      <c r="P16" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" t="s">
+        <v>29</v>
+      </c>
+      <c r="S16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="I17" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17">
+        <v>10</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" t="s">
+        <v>109</v>
+      </c>
+      <c r="P17" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>28</v>
+      </c>
+      <c r="R17" t="s">
+        <v>29</v>
+      </c>
+      <c r="S17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>10</v>
+      </c>
+      <c r="N18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" t="s">
+        <v>112</v>
+      </c>
+      <c r="P18" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>28</v>
+      </c>
+      <c r="R18" t="s">
+        <v>29</v>
+      </c>
+      <c r="S18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+      <c r="M19">
+        <v>10</v>
+      </c>
+      <c r="N19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" t="s">
+        <v>115</v>
+      </c>
+      <c r="P19" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>29</v>
+      </c>
+      <c r="S19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" t="s">
+        <v>44</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L20">
+        <v>10</v>
+      </c>
+      <c r="M20">
+        <v>10</v>
+      </c>
+      <c r="N20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" t="s">
+        <v>118</v>
+      </c>
+      <c r="P20" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" t="s">
+        <v>29</v>
+      </c>
+      <c r="S20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" t="s">
+        <v>105</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+      <c r="M21">
+        <v>5</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" t="s">
+        <v>121</v>
+      </c>
+      <c r="P21" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>28</v>
+      </c>
+      <c r="R21" t="s">
+        <v>29</v>
+      </c>
+      <c r="S21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" t="s">
+        <v>125</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" t="s">
+        <v>40</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22">
+        <v>6</v>
+      </c>
+      <c r="M22">
+        <v>6</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" t="s">
+        <v>126</v>
+      </c>
+      <c r="P22" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" t="s">
         <v>16</v>
       </c>
-      <c r="H3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="I23" t="s">
+        <v>41</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23">
+        <v>5.5</v>
+      </c>
+      <c r="M23">
+        <v>5.5</v>
+      </c>
+      <c r="N23" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="O23" t="s">
+        <v>129</v>
+      </c>
+      <c r="P23" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q23" t="s">
         <v>28</v>
+      </c>
+      <c r="R23" t="s">
+        <v>29</v>
+      </c>
+      <c r="S23" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
